--- a/01. BaseTraining/unit2_file/unit2_file.xlsx
+++ b/01. BaseTraining/unit2_file/unit2_file.xlsx
@@ -7550,8 +7550,17 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -7559,26 +7568,17 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10003,57 +10003,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:80" ht="15" customHeight="1">
-      <c r="D2" s="119" t="s">
+      <c r="D2" s="116" t="s">
         <v>264</v>
       </c>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119" t="s">
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116" t="s">
         <v>265</v>
       </c>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119" t="s">
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116" t="s">
         <v>266</v>
       </c>
-      <c r="W2" s="119"/>
-      <c r="X2" s="119"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="119"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="119"/>
-      <c r="AD2" s="119"/>
-      <c r="AE2" s="119"/>
-      <c r="AF2" s="119"/>
-      <c r="AG2" s="119"/>
-      <c r="AH2" s="119"/>
-      <c r="AI2" s="119"/>
-      <c r="AJ2" s="119"/>
-      <c r="AK2" s="119"/>
-      <c r="AL2" s="119"/>
-      <c r="AM2" s="119"/>
-      <c r="AN2" s="119"/>
-      <c r="AO2" s="119"/>
-      <c r="AP2" s="119"/>
-      <c r="AQ2" s="119"/>
-      <c r="AR2" s="119"/>
-      <c r="AS2" s="119"/>
-      <c r="AT2" s="119"/>
-      <c r="AU2" s="119"/>
-      <c r="AV2" s="119"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
+      <c r="AE2" s="116"/>
+      <c r="AF2" s="116"/>
+      <c r="AG2" s="116"/>
+      <c r="AH2" s="116"/>
+      <c r="AI2" s="116"/>
+      <c r="AJ2" s="116"/>
+      <c r="AK2" s="116"/>
+      <c r="AL2" s="116"/>
+      <c r="AM2" s="116"/>
+      <c r="AN2" s="116"/>
+      <c r="AO2" s="116"/>
+      <c r="AP2" s="116"/>
+      <c r="AQ2" s="116"/>
+      <c r="AR2" s="116"/>
+      <c r="AS2" s="116"/>
+      <c r="AT2" s="116"/>
+      <c r="AU2" s="116"/>
+      <c r="AV2" s="116"/>
     </row>
     <row r="3" spans="4:80" ht="15" customHeight="1">
       <c r="D3" s="118" t="s">
@@ -10062,51 +10062,51 @@
       <c r="E3" s="118"/>
       <c r="F3" s="118"/>
       <c r="G3" s="118"/>
-      <c r="H3" s="120" t="s">
+      <c r="H3" s="115" t="s">
         <v>268</v>
       </c>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="120"/>
-      <c r="O3" s="120"/>
-      <c r="P3" s="120"/>
-      <c r="Q3" s="120"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
-      <c r="T3" s="120"/>
-      <c r="U3" s="120"/>
-      <c r="V3" s="120" t="s">
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="115"/>
+      <c r="T3" s="115"/>
+      <c r="U3" s="115"/>
+      <c r="V3" s="115" t="s">
         <v>269</v>
       </c>
-      <c r="W3" s="120"/>
-      <c r="X3" s="120"/>
-      <c r="Y3" s="120"/>
-      <c r="Z3" s="120"/>
-      <c r="AA3" s="120"/>
-      <c r="AB3" s="120"/>
-      <c r="AC3" s="120"/>
-      <c r="AD3" s="120"/>
-      <c r="AE3" s="120"/>
-      <c r="AF3" s="120"/>
-      <c r="AG3" s="120"/>
-      <c r="AH3" s="120"/>
-      <c r="AI3" s="120"/>
-      <c r="AJ3" s="120"/>
-      <c r="AK3" s="120"/>
-      <c r="AL3" s="120"/>
-      <c r="AM3" s="120"/>
-      <c r="AN3" s="120"/>
-      <c r="AO3" s="120"/>
-      <c r="AP3" s="120"/>
-      <c r="AQ3" s="120"/>
-      <c r="AR3" s="120"/>
-      <c r="AS3" s="120"/>
-      <c r="AT3" s="120"/>
-      <c r="AU3" s="120"/>
-      <c r="AV3" s="120"/>
+      <c r="W3" s="115"/>
+      <c r="X3" s="115"/>
+      <c r="Y3" s="115"/>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
+      <c r="AE3" s="115"/>
+      <c r="AF3" s="115"/>
+      <c r="AG3" s="115"/>
+      <c r="AH3" s="115"/>
+      <c r="AI3" s="115"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="115"/>
+      <c r="AP3" s="115"/>
+      <c r="AQ3" s="115"/>
+      <c r="AR3" s="115"/>
+      <c r="AS3" s="115"/>
+      <c r="AT3" s="115"/>
+      <c r="AU3" s="115"/>
+      <c r="AV3" s="115"/>
     </row>
     <row r="4" spans="4:80" ht="15" customHeight="1">
       <c r="D4" s="118" t="s">
@@ -10115,51 +10115,51 @@
       <c r="E4" s="118"/>
       <c r="F4" s="118"/>
       <c r="G4" s="118"/>
-      <c r="H4" s="121" t="s">
+      <c r="H4" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121"/>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121"/>
-      <c r="V4" s="120" t="s">
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="115" t="s">
         <v>272</v>
       </c>
-      <c r="W4" s="120"/>
-      <c r="X4" s="120"/>
-      <c r="Y4" s="120"/>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="120"/>
-      <c r="AE4" s="120"/>
-      <c r="AF4" s="120"/>
-      <c r="AG4" s="120"/>
-      <c r="AH4" s="120"/>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="120"/>
-      <c r="AK4" s="120"/>
-      <c r="AL4" s="120"/>
-      <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
-      <c r="AO4" s="120"/>
-      <c r="AP4" s="120"/>
-      <c r="AQ4" s="120"/>
-      <c r="AR4" s="120"/>
-      <c r="AS4" s="120"/>
-      <c r="AT4" s="120"/>
-      <c r="AU4" s="120"/>
-      <c r="AV4" s="120"/>
+      <c r="W4" s="115"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="115"/>
+      <c r="AQ4" s="115"/>
+      <c r="AR4" s="115"/>
+      <c r="AS4" s="115"/>
+      <c r="AT4" s="115"/>
+      <c r="AU4" s="115"/>
+      <c r="AV4" s="115"/>
     </row>
     <row r="5" spans="4:80" ht="15" customHeight="1">
       <c r="D5" s="118" t="s">
@@ -10168,51 +10168,51 @@
       <c r="E5" s="118"/>
       <c r="F5" s="118"/>
       <c r="G5" s="118"/>
-      <c r="H5" s="121" t="s">
+      <c r="H5" s="117" t="s">
         <v>274</v>
       </c>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
-      <c r="O5" s="121"/>
-      <c r="P5" s="121"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="121"/>
-      <c r="S5" s="121"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="120" t="s">
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="115" t="s">
         <v>275</v>
       </c>
-      <c r="W5" s="120"/>
-      <c r="X5" s="120"/>
-      <c r="Y5" s="120"/>
-      <c r="Z5" s="120"/>
-      <c r="AA5" s="120"/>
-      <c r="AB5" s="120"/>
-      <c r="AC5" s="120"/>
-      <c r="AD5" s="120"/>
-      <c r="AE5" s="120"/>
-      <c r="AF5" s="120"/>
-      <c r="AG5" s="120"/>
-      <c r="AH5" s="120"/>
-      <c r="AI5" s="120"/>
-      <c r="AJ5" s="120"/>
-      <c r="AK5" s="120"/>
-      <c r="AL5" s="120"/>
-      <c r="AM5" s="120"/>
-      <c r="AN5" s="120"/>
-      <c r="AO5" s="120"/>
-      <c r="AP5" s="120"/>
-      <c r="AQ5" s="120"/>
-      <c r="AR5" s="120"/>
-      <c r="AS5" s="120"/>
-      <c r="AT5" s="120"/>
-      <c r="AU5" s="120"/>
-      <c r="AV5" s="120"/>
+      <c r="W5" s="115"/>
+      <c r="X5" s="115"/>
+      <c r="Y5" s="115"/>
+      <c r="Z5" s="115"/>
+      <c r="AA5" s="115"/>
+      <c r="AB5" s="115"/>
+      <c r="AC5" s="115"/>
+      <c r="AD5" s="115"/>
+      <c r="AE5" s="115"/>
+      <c r="AF5" s="115"/>
+      <c r="AG5" s="115"/>
+      <c r="AH5" s="115"/>
+      <c r="AI5" s="115"/>
+      <c r="AJ5" s="115"/>
+      <c r="AK5" s="115"/>
+      <c r="AL5" s="115"/>
+      <c r="AM5" s="115"/>
+      <c r="AN5" s="115"/>
+      <c r="AO5" s="115"/>
+      <c r="AP5" s="115"/>
+      <c r="AQ5" s="115"/>
+      <c r="AR5" s="115"/>
+      <c r="AS5" s="115"/>
+      <c r="AT5" s="115"/>
+      <c r="AU5" s="115"/>
+      <c r="AV5" s="115"/>
     </row>
     <row r="6" spans="4:80" ht="15" customHeight="1">
       <c r="D6" s="118" t="s">
@@ -10221,86 +10221,86 @@
       <c r="E6" s="118"/>
       <c r="F6" s="118"/>
       <c r="G6" s="118"/>
-      <c r="H6" s="120" t="s">
+      <c r="H6" s="115" t="s">
         <v>277</v>
       </c>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
-      <c r="L6" s="120"/>
-      <c r="M6" s="120"/>
-      <c r="N6" s="120"/>
-      <c r="O6" s="120"/>
-      <c r="P6" s="120"/>
-      <c r="Q6" s="120"/>
-      <c r="R6" s="120"/>
-      <c r="S6" s="120"/>
-      <c r="T6" s="120"/>
-      <c r="U6" s="120"/>
-      <c r="V6" s="120" t="s">
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115"/>
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115" t="s">
         <v>278</v>
       </c>
-      <c r="W6" s="120"/>
-      <c r="X6" s="120"/>
-      <c r="Y6" s="120"/>
-      <c r="Z6" s="120"/>
-      <c r="AA6" s="120"/>
-      <c r="AB6" s="120"/>
-      <c r="AC6" s="120"/>
-      <c r="AD6" s="120"/>
-      <c r="AE6" s="120"/>
-      <c r="AF6" s="120"/>
-      <c r="AG6" s="120"/>
-      <c r="AH6" s="120"/>
-      <c r="AI6" s="120"/>
-      <c r="AJ6" s="120"/>
-      <c r="AK6" s="120"/>
-      <c r="AL6" s="120"/>
-      <c r="AM6" s="120"/>
-      <c r="AN6" s="120"/>
-      <c r="AO6" s="120"/>
-      <c r="AP6" s="120"/>
-      <c r="AQ6" s="120"/>
-      <c r="AR6" s="120"/>
-      <c r="AS6" s="120"/>
-      <c r="AT6" s="120"/>
-      <c r="AU6" s="120"/>
-      <c r="AV6" s="120"/>
-      <c r="AZ6" s="115" t="s">
+      <c r="W6" s="115"/>
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115"/>
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
+      <c r="AE6" s="115"/>
+      <c r="AF6" s="115"/>
+      <c r="AG6" s="115"/>
+      <c r="AH6" s="115"/>
+      <c r="AI6" s="115"/>
+      <c r="AJ6" s="115"/>
+      <c r="AK6" s="115"/>
+      <c r="AL6" s="115"/>
+      <c r="AM6" s="115"/>
+      <c r="AN6" s="115"/>
+      <c r="AO6" s="115"/>
+      <c r="AP6" s="115"/>
+      <c r="AQ6" s="115"/>
+      <c r="AR6" s="115"/>
+      <c r="AS6" s="115"/>
+      <c r="AT6" s="115"/>
+      <c r="AU6" s="115"/>
+      <c r="AV6" s="115"/>
+      <c r="AZ6" s="121" t="s">
         <v>329</v>
       </c>
-      <c r="BA6" s="115"/>
-      <c r="BB6" s="115"/>
-      <c r="BC6" s="115"/>
-      <c r="BD6" s="115"/>
-      <c r="BE6" s="115" t="s">
+      <c r="BA6" s="121"/>
+      <c r="BB6" s="121"/>
+      <c r="BC6" s="121"/>
+      <c r="BD6" s="121"/>
+      <c r="BE6" s="121" t="s">
         <v>330</v>
       </c>
-      <c r="BF6" s="115"/>
-      <c r="BG6" s="115"/>
-      <c r="BH6" s="115"/>
-      <c r="BI6" s="115"/>
-      <c r="BJ6" s="115"/>
-      <c r="BK6" s="115"/>
-      <c r="BL6" s="115"/>
-      <c r="BM6" s="115"/>
-      <c r="BN6" s="115" t="s">
+      <c r="BF6" s="121"/>
+      <c r="BG6" s="121"/>
+      <c r="BH6" s="121"/>
+      <c r="BI6" s="121"/>
+      <c r="BJ6" s="121"/>
+      <c r="BK6" s="121"/>
+      <c r="BL6" s="121"/>
+      <c r="BM6" s="121"/>
+      <c r="BN6" s="121" t="s">
         <v>331</v>
       </c>
-      <c r="BO6" s="115"/>
-      <c r="BP6" s="115"/>
-      <c r="BQ6" s="115"/>
-      <c r="BR6" s="115"/>
-      <c r="BS6" s="115"/>
-      <c r="BT6" s="115"/>
-      <c r="BU6" s="115"/>
-      <c r="BV6" s="115"/>
-      <c r="BW6" s="115"/>
-      <c r="BX6" s="115"/>
-      <c r="BY6" s="115"/>
-      <c r="BZ6" s="115"/>
-      <c r="CA6" s="115"/>
-      <c r="CB6" s="115"/>
+      <c r="BO6" s="121"/>
+      <c r="BP6" s="121"/>
+      <c r="BQ6" s="121"/>
+      <c r="BR6" s="121"/>
+      <c r="BS6" s="121"/>
+      <c r="BT6" s="121"/>
+      <c r="BU6" s="121"/>
+      <c r="BV6" s="121"/>
+      <c r="BW6" s="121"/>
+      <c r="BX6" s="121"/>
+      <c r="BY6" s="121"/>
+      <c r="BZ6" s="121"/>
+      <c r="CA6" s="121"/>
+      <c r="CB6" s="121"/>
     </row>
     <row r="7" spans="4:80" ht="15" customHeight="1">
       <c r="D7" s="118" t="s">
@@ -10309,86 +10309,86 @@
       <c r="E7" s="118"/>
       <c r="F7" s="118"/>
       <c r="G7" s="118"/>
-      <c r="H7" s="121" t="s">
+      <c r="H7" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="I7" s="121"/>
-      <c r="J7" s="121"/>
-      <c r="K7" s="121"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="121"/>
-      <c r="N7" s="121"/>
-      <c r="O7" s="121"/>
-      <c r="P7" s="121"/>
-      <c r="Q7" s="121"/>
-      <c r="R7" s="121"/>
-      <c r="S7" s="121"/>
-      <c r="T7" s="121"/>
-      <c r="U7" s="121"/>
-      <c r="V7" s="120" t="s">
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="117"/>
+      <c r="M7" s="117"/>
+      <c r="N7" s="117"/>
+      <c r="O7" s="117"/>
+      <c r="P7" s="117"/>
+      <c r="Q7" s="117"/>
+      <c r="R7" s="117"/>
+      <c r="S7" s="117"/>
+      <c r="T7" s="117"/>
+      <c r="U7" s="117"/>
+      <c r="V7" s="115" t="s">
         <v>281</v>
       </c>
-      <c r="W7" s="120"/>
-      <c r="X7" s="120"/>
-      <c r="Y7" s="120"/>
-      <c r="Z7" s="120"/>
-      <c r="AA7" s="120"/>
-      <c r="AB7" s="120"/>
-      <c r="AC7" s="120"/>
-      <c r="AD7" s="120"/>
-      <c r="AE7" s="120"/>
-      <c r="AF7" s="120"/>
-      <c r="AG7" s="120"/>
-      <c r="AH7" s="120"/>
-      <c r="AI7" s="120"/>
-      <c r="AJ7" s="120"/>
-      <c r="AK7" s="120"/>
-      <c r="AL7" s="120"/>
-      <c r="AM7" s="120"/>
-      <c r="AN7" s="120"/>
-      <c r="AO7" s="120"/>
-      <c r="AP7" s="120"/>
-      <c r="AQ7" s="120"/>
-      <c r="AR7" s="120"/>
-      <c r="AS7" s="120"/>
-      <c r="AT7" s="120"/>
-      <c r="AU7" s="120"/>
-      <c r="AV7" s="120"/>
-      <c r="AZ7" s="117" t="s">
+      <c r="W7" s="115"/>
+      <c r="X7" s="115"/>
+      <c r="Y7" s="115"/>
+      <c r="Z7" s="115"/>
+      <c r="AA7" s="115"/>
+      <c r="AB7" s="115"/>
+      <c r="AC7" s="115"/>
+      <c r="AD7" s="115"/>
+      <c r="AE7" s="115"/>
+      <c r="AF7" s="115"/>
+      <c r="AG7" s="115"/>
+      <c r="AH7" s="115"/>
+      <c r="AI7" s="115"/>
+      <c r="AJ7" s="115"/>
+      <c r="AK7" s="115"/>
+      <c r="AL7" s="115"/>
+      <c r="AM7" s="115"/>
+      <c r="AN7" s="115"/>
+      <c r="AO7" s="115"/>
+      <c r="AP7" s="115"/>
+      <c r="AQ7" s="115"/>
+      <c r="AR7" s="115"/>
+      <c r="AS7" s="115"/>
+      <c r="AT7" s="115"/>
+      <c r="AU7" s="115"/>
+      <c r="AV7" s="115"/>
+      <c r="AZ7" s="120" t="s">
         <v>324</v>
       </c>
-      <c r="BA7" s="117"/>
-      <c r="BB7" s="117"/>
-      <c r="BC7" s="117"/>
-      <c r="BD7" s="117"/>
-      <c r="BE7" s="116" t="s">
+      <c r="BA7" s="120"/>
+      <c r="BB7" s="120"/>
+      <c r="BC7" s="120"/>
+      <c r="BD7" s="120"/>
+      <c r="BE7" s="119" t="s">
         <v>332</v>
       </c>
-      <c r="BF7" s="116"/>
-      <c r="BG7" s="116"/>
-      <c r="BH7" s="116"/>
-      <c r="BI7" s="116"/>
-      <c r="BJ7" s="116"/>
-      <c r="BK7" s="116"/>
-      <c r="BL7" s="116"/>
-      <c r="BM7" s="116"/>
-      <c r="BN7" s="116" t="s">
+      <c r="BF7" s="119"/>
+      <c r="BG7" s="119"/>
+      <c r="BH7" s="119"/>
+      <c r="BI7" s="119"/>
+      <c r="BJ7" s="119"/>
+      <c r="BK7" s="119"/>
+      <c r="BL7" s="119"/>
+      <c r="BM7" s="119"/>
+      <c r="BN7" s="119" t="s">
         <v>333</v>
       </c>
-      <c r="BO7" s="116"/>
-      <c r="BP7" s="116"/>
-      <c r="BQ7" s="116"/>
-      <c r="BR7" s="116"/>
-      <c r="BS7" s="116"/>
-      <c r="BT7" s="116"/>
-      <c r="BU7" s="116"/>
-      <c r="BV7" s="116"/>
-      <c r="BW7" s="116"/>
-      <c r="BX7" s="116"/>
-      <c r="BY7" s="116"/>
-      <c r="BZ7" s="116"/>
-      <c r="CA7" s="116"/>
-      <c r="CB7" s="116"/>
+      <c r="BO7" s="119"/>
+      <c r="BP7" s="119"/>
+      <c r="BQ7" s="119"/>
+      <c r="BR7" s="119"/>
+      <c r="BS7" s="119"/>
+      <c r="BT7" s="119"/>
+      <c r="BU7" s="119"/>
+      <c r="BV7" s="119"/>
+      <c r="BW7" s="119"/>
+      <c r="BX7" s="119"/>
+      <c r="BY7" s="119"/>
+      <c r="BZ7" s="119"/>
+      <c r="CA7" s="119"/>
+      <c r="CB7" s="119"/>
     </row>
     <row r="8" spans="4:80" ht="15" customHeight="1">
       <c r="D8" s="118" t="s">
@@ -10397,86 +10397,86 @@
       <c r="E8" s="118"/>
       <c r="F8" s="118"/>
       <c r="G8" s="118"/>
-      <c r="H8" s="121" t="s">
+      <c r="H8" s="117" t="s">
         <v>283</v>
       </c>
-      <c r="I8" s="121"/>
-      <c r="J8" s="121"/>
-      <c r="K8" s="121"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="121"/>
-      <c r="O8" s="121"/>
-      <c r="P8" s="121"/>
-      <c r="Q8" s="121"/>
-      <c r="R8" s="121"/>
-      <c r="S8" s="121"/>
-      <c r="T8" s="121"/>
-      <c r="U8" s="121"/>
-      <c r="V8" s="120" t="s">
+      <c r="I8" s="117"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="117"/>
+      <c r="O8" s="117"/>
+      <c r="P8" s="117"/>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117"/>
+      <c r="S8" s="117"/>
+      <c r="T8" s="117"/>
+      <c r="U8" s="117"/>
+      <c r="V8" s="115" t="s">
         <v>284</v>
       </c>
-      <c r="W8" s="120"/>
-      <c r="X8" s="120"/>
-      <c r="Y8" s="120"/>
-      <c r="Z8" s="120"/>
-      <c r="AA8" s="120"/>
-      <c r="AB8" s="120"/>
-      <c r="AC8" s="120"/>
-      <c r="AD8" s="120"/>
-      <c r="AE8" s="120"/>
-      <c r="AF8" s="120"/>
-      <c r="AG8" s="120"/>
-      <c r="AH8" s="120"/>
-      <c r="AI8" s="120"/>
-      <c r="AJ8" s="120"/>
-      <c r="AK8" s="120"/>
-      <c r="AL8" s="120"/>
-      <c r="AM8" s="120"/>
-      <c r="AN8" s="120"/>
-      <c r="AO8" s="120"/>
-      <c r="AP8" s="120"/>
-      <c r="AQ8" s="120"/>
-      <c r="AR8" s="120"/>
-      <c r="AS8" s="120"/>
-      <c r="AT8" s="120"/>
-      <c r="AU8" s="120"/>
-      <c r="AV8" s="120"/>
-      <c r="AZ8" s="117" t="s">
+      <c r="W8" s="115"/>
+      <c r="X8" s="115"/>
+      <c r="Y8" s="115"/>
+      <c r="Z8" s="115"/>
+      <c r="AA8" s="115"/>
+      <c r="AB8" s="115"/>
+      <c r="AC8" s="115"/>
+      <c r="AD8" s="115"/>
+      <c r="AE8" s="115"/>
+      <c r="AF8" s="115"/>
+      <c r="AG8" s="115"/>
+      <c r="AH8" s="115"/>
+      <c r="AI8" s="115"/>
+      <c r="AJ8" s="115"/>
+      <c r="AK8" s="115"/>
+      <c r="AL8" s="115"/>
+      <c r="AM8" s="115"/>
+      <c r="AN8" s="115"/>
+      <c r="AO8" s="115"/>
+      <c r="AP8" s="115"/>
+      <c r="AQ8" s="115"/>
+      <c r="AR8" s="115"/>
+      <c r="AS8" s="115"/>
+      <c r="AT8" s="115"/>
+      <c r="AU8" s="115"/>
+      <c r="AV8" s="115"/>
+      <c r="AZ8" s="120" t="s">
         <v>325</v>
       </c>
-      <c r="BA8" s="117"/>
-      <c r="BB8" s="117"/>
-      <c r="BC8" s="117"/>
-      <c r="BD8" s="117"/>
-      <c r="BE8" s="116" t="s">
+      <c r="BA8" s="120"/>
+      <c r="BB8" s="120"/>
+      <c r="BC8" s="120"/>
+      <c r="BD8" s="120"/>
+      <c r="BE8" s="119" t="s">
         <v>328</v>
       </c>
-      <c r="BF8" s="116"/>
-      <c r="BG8" s="116"/>
-      <c r="BH8" s="116"/>
-      <c r="BI8" s="116"/>
-      <c r="BJ8" s="116"/>
-      <c r="BK8" s="116"/>
-      <c r="BL8" s="116"/>
-      <c r="BM8" s="116"/>
-      <c r="BN8" s="116" t="s">
+      <c r="BF8" s="119"/>
+      <c r="BG8" s="119"/>
+      <c r="BH8" s="119"/>
+      <c r="BI8" s="119"/>
+      <c r="BJ8" s="119"/>
+      <c r="BK8" s="119"/>
+      <c r="BL8" s="119"/>
+      <c r="BM8" s="119"/>
+      <c r="BN8" s="119" t="s">
         <v>334</v>
       </c>
-      <c r="BO8" s="116"/>
-      <c r="BP8" s="116"/>
-      <c r="BQ8" s="116"/>
-      <c r="BR8" s="116"/>
-      <c r="BS8" s="116"/>
-      <c r="BT8" s="116"/>
-      <c r="BU8" s="116"/>
-      <c r="BV8" s="116"/>
-      <c r="BW8" s="116"/>
-      <c r="BX8" s="116"/>
-      <c r="BY8" s="116"/>
-      <c r="BZ8" s="116"/>
-      <c r="CA8" s="116"/>
-      <c r="CB8" s="116"/>
+      <c r="BO8" s="119"/>
+      <c r="BP8" s="119"/>
+      <c r="BQ8" s="119"/>
+      <c r="BR8" s="119"/>
+      <c r="BS8" s="119"/>
+      <c r="BT8" s="119"/>
+      <c r="BU8" s="119"/>
+      <c r="BV8" s="119"/>
+      <c r="BW8" s="119"/>
+      <c r="BX8" s="119"/>
+      <c r="BY8" s="119"/>
+      <c r="BZ8" s="119"/>
+      <c r="CA8" s="119"/>
+      <c r="CB8" s="119"/>
     </row>
     <row r="9" spans="4:80" ht="15" customHeight="1">
       <c r="D9" s="118" t="s">
@@ -10485,86 +10485,86 @@
       <c r="E9" s="118"/>
       <c r="F9" s="118"/>
       <c r="G9" s="118"/>
-      <c r="H9" s="120" t="s">
+      <c r="H9" s="115" t="s">
         <v>286</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="120"/>
-      <c r="O9" s="120"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="120"/>
-      <c r="R9" s="120"/>
-      <c r="S9" s="120"/>
-      <c r="T9" s="120"/>
-      <c r="U9" s="120"/>
-      <c r="V9" s="120" t="s">
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="115"/>
+      <c r="O9" s="115"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
+      <c r="S9" s="115"/>
+      <c r="T9" s="115"/>
+      <c r="U9" s="115"/>
+      <c r="V9" s="115" t="s">
         <v>287</v>
       </c>
-      <c r="W9" s="120"/>
-      <c r="X9" s="120"/>
-      <c r="Y9" s="120"/>
-      <c r="Z9" s="120"/>
-      <c r="AA9" s="120"/>
-      <c r="AB9" s="120"/>
-      <c r="AC9" s="120"/>
-      <c r="AD9" s="120"/>
-      <c r="AE9" s="120"/>
-      <c r="AF9" s="120"/>
-      <c r="AG9" s="120"/>
-      <c r="AH9" s="120"/>
-      <c r="AI9" s="120"/>
-      <c r="AJ9" s="120"/>
-      <c r="AK9" s="120"/>
-      <c r="AL9" s="120"/>
-      <c r="AM9" s="120"/>
-      <c r="AN9" s="120"/>
-      <c r="AO9" s="120"/>
-      <c r="AP9" s="120"/>
-      <c r="AQ9" s="120"/>
-      <c r="AR9" s="120"/>
-      <c r="AS9" s="120"/>
-      <c r="AT9" s="120"/>
-      <c r="AU9" s="120"/>
-      <c r="AV9" s="120"/>
-      <c r="AZ9" s="117" t="s">
+      <c r="W9" s="115"/>
+      <c r="X9" s="115"/>
+      <c r="Y9" s="115"/>
+      <c r="Z9" s="115"/>
+      <c r="AA9" s="115"/>
+      <c r="AB9" s="115"/>
+      <c r="AC9" s="115"/>
+      <c r="AD9" s="115"/>
+      <c r="AE9" s="115"/>
+      <c r="AF9" s="115"/>
+      <c r="AG9" s="115"/>
+      <c r="AH9" s="115"/>
+      <c r="AI9" s="115"/>
+      <c r="AJ9" s="115"/>
+      <c r="AK9" s="115"/>
+      <c r="AL9" s="115"/>
+      <c r="AM9" s="115"/>
+      <c r="AN9" s="115"/>
+      <c r="AO9" s="115"/>
+      <c r="AP9" s="115"/>
+      <c r="AQ9" s="115"/>
+      <c r="AR9" s="115"/>
+      <c r="AS9" s="115"/>
+      <c r="AT9" s="115"/>
+      <c r="AU9" s="115"/>
+      <c r="AV9" s="115"/>
+      <c r="AZ9" s="120" t="s">
         <v>326</v>
       </c>
-      <c r="BA9" s="117"/>
-      <c r="BB9" s="117"/>
-      <c r="BC9" s="117"/>
-      <c r="BD9" s="117"/>
-      <c r="BE9" s="116" t="s">
+      <c r="BA9" s="120"/>
+      <c r="BB9" s="120"/>
+      <c r="BC9" s="120"/>
+      <c r="BD9" s="120"/>
+      <c r="BE9" s="119" t="s">
         <v>335</v>
       </c>
-      <c r="BF9" s="116"/>
-      <c r="BG9" s="116"/>
-      <c r="BH9" s="116"/>
-      <c r="BI9" s="116"/>
-      <c r="BJ9" s="116"/>
-      <c r="BK9" s="116"/>
-      <c r="BL9" s="116"/>
-      <c r="BM9" s="116"/>
-      <c r="BN9" s="116" t="s">
+      <c r="BF9" s="119"/>
+      <c r="BG9" s="119"/>
+      <c r="BH9" s="119"/>
+      <c r="BI9" s="119"/>
+      <c r="BJ9" s="119"/>
+      <c r="BK9" s="119"/>
+      <c r="BL9" s="119"/>
+      <c r="BM9" s="119"/>
+      <c r="BN9" s="119" t="s">
         <v>336</v>
       </c>
-      <c r="BO9" s="116"/>
-      <c r="BP9" s="116"/>
-      <c r="BQ9" s="116"/>
-      <c r="BR9" s="116"/>
-      <c r="BS9" s="116"/>
-      <c r="BT9" s="116"/>
-      <c r="BU9" s="116"/>
-      <c r="BV9" s="116"/>
-      <c r="BW9" s="116"/>
-      <c r="BX9" s="116"/>
-      <c r="BY9" s="116"/>
-      <c r="BZ9" s="116"/>
-      <c r="CA9" s="116"/>
-      <c r="CB9" s="116"/>
+      <c r="BO9" s="119"/>
+      <c r="BP9" s="119"/>
+      <c r="BQ9" s="119"/>
+      <c r="BR9" s="119"/>
+      <c r="BS9" s="119"/>
+      <c r="BT9" s="119"/>
+      <c r="BU9" s="119"/>
+      <c r="BV9" s="119"/>
+      <c r="BW9" s="119"/>
+      <c r="BX9" s="119"/>
+      <c r="BY9" s="119"/>
+      <c r="BZ9" s="119"/>
+      <c r="CA9" s="119"/>
+      <c r="CB9" s="119"/>
     </row>
     <row r="10" spans="4:80" ht="15" customHeight="1">
       <c r="D10" s="118" t="s">
@@ -10573,86 +10573,86 @@
       <c r="E10" s="118"/>
       <c r="F10" s="118"/>
       <c r="G10" s="118"/>
-      <c r="H10" s="121" t="s">
+      <c r="H10" s="117" t="s">
         <v>289</v>
       </c>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="121"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
-      <c r="O10" s="121"/>
-      <c r="P10" s="121"/>
-      <c r="Q10" s="121"/>
-      <c r="R10" s="121"/>
-      <c r="S10" s="121"/>
-      <c r="T10" s="121"/>
-      <c r="U10" s="121"/>
-      <c r="V10" s="120" t="s">
+      <c r="I10" s="117"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="117"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="117"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="117"/>
+      <c r="S10" s="117"/>
+      <c r="T10" s="117"/>
+      <c r="U10" s="117"/>
+      <c r="V10" s="115" t="s">
         <v>290</v>
       </c>
-      <c r="W10" s="120"/>
-      <c r="X10" s="120"/>
-      <c r="Y10" s="120"/>
-      <c r="Z10" s="120"/>
-      <c r="AA10" s="120"/>
-      <c r="AB10" s="120"/>
-      <c r="AC10" s="120"/>
-      <c r="AD10" s="120"/>
-      <c r="AE10" s="120"/>
-      <c r="AF10" s="120"/>
-      <c r="AG10" s="120"/>
-      <c r="AH10" s="120"/>
-      <c r="AI10" s="120"/>
-      <c r="AJ10" s="120"/>
-      <c r="AK10" s="120"/>
-      <c r="AL10" s="120"/>
-      <c r="AM10" s="120"/>
-      <c r="AN10" s="120"/>
-      <c r="AO10" s="120"/>
-      <c r="AP10" s="120"/>
-      <c r="AQ10" s="120"/>
-      <c r="AR10" s="120"/>
-      <c r="AS10" s="120"/>
-      <c r="AT10" s="120"/>
-      <c r="AU10" s="120"/>
-      <c r="AV10" s="120"/>
-      <c r="AZ10" s="117" t="s">
+      <c r="W10" s="115"/>
+      <c r="X10" s="115"/>
+      <c r="Y10" s="115"/>
+      <c r="Z10" s="115"/>
+      <c r="AA10" s="115"/>
+      <c r="AB10" s="115"/>
+      <c r="AC10" s="115"/>
+      <c r="AD10" s="115"/>
+      <c r="AE10" s="115"/>
+      <c r="AF10" s="115"/>
+      <c r="AG10" s="115"/>
+      <c r="AH10" s="115"/>
+      <c r="AI10" s="115"/>
+      <c r="AJ10" s="115"/>
+      <c r="AK10" s="115"/>
+      <c r="AL10" s="115"/>
+      <c r="AM10" s="115"/>
+      <c r="AN10" s="115"/>
+      <c r="AO10" s="115"/>
+      <c r="AP10" s="115"/>
+      <c r="AQ10" s="115"/>
+      <c r="AR10" s="115"/>
+      <c r="AS10" s="115"/>
+      <c r="AT10" s="115"/>
+      <c r="AU10" s="115"/>
+      <c r="AV10" s="115"/>
+      <c r="AZ10" s="120" t="s">
         <v>147</v>
       </c>
-      <c r="BA10" s="117"/>
-      <c r="BB10" s="117"/>
-      <c r="BC10" s="117"/>
-      <c r="BD10" s="117"/>
-      <c r="BE10" s="116" t="s">
+      <c r="BA10" s="120"/>
+      <c r="BB10" s="120"/>
+      <c r="BC10" s="120"/>
+      <c r="BD10" s="120"/>
+      <c r="BE10" s="119" t="s">
         <v>337</v>
       </c>
-      <c r="BF10" s="116"/>
-      <c r="BG10" s="116"/>
-      <c r="BH10" s="116"/>
-      <c r="BI10" s="116"/>
-      <c r="BJ10" s="116"/>
-      <c r="BK10" s="116"/>
-      <c r="BL10" s="116"/>
-      <c r="BM10" s="116"/>
-      <c r="BN10" s="116" t="s">
+      <c r="BF10" s="119"/>
+      <c r="BG10" s="119"/>
+      <c r="BH10" s="119"/>
+      <c r="BI10" s="119"/>
+      <c r="BJ10" s="119"/>
+      <c r="BK10" s="119"/>
+      <c r="BL10" s="119"/>
+      <c r="BM10" s="119"/>
+      <c r="BN10" s="119" t="s">
         <v>338</v>
       </c>
-      <c r="BO10" s="116"/>
-      <c r="BP10" s="116"/>
-      <c r="BQ10" s="116"/>
-      <c r="BR10" s="116"/>
-      <c r="BS10" s="116"/>
-      <c r="BT10" s="116"/>
-      <c r="BU10" s="116"/>
-      <c r="BV10" s="116"/>
-      <c r="BW10" s="116"/>
-      <c r="BX10" s="116"/>
-      <c r="BY10" s="116"/>
-      <c r="BZ10" s="116"/>
-      <c r="CA10" s="116"/>
-      <c r="CB10" s="116"/>
+      <c r="BO10" s="119"/>
+      <c r="BP10" s="119"/>
+      <c r="BQ10" s="119"/>
+      <c r="BR10" s="119"/>
+      <c r="BS10" s="119"/>
+      <c r="BT10" s="119"/>
+      <c r="BU10" s="119"/>
+      <c r="BV10" s="119"/>
+      <c r="BW10" s="119"/>
+      <c r="BX10" s="119"/>
+      <c r="BY10" s="119"/>
+      <c r="BZ10" s="119"/>
+      <c r="CA10" s="119"/>
+      <c r="CB10" s="119"/>
     </row>
     <row r="11" spans="4:80" ht="15" customHeight="1">
       <c r="D11" s="118" t="s">
@@ -10661,86 +10661,86 @@
       <c r="E11" s="118"/>
       <c r="F11" s="118"/>
       <c r="G11" s="118"/>
-      <c r="H11" s="120" t="s">
+      <c r="H11" s="115" t="s">
         <v>292</v>
       </c>
-      <c r="I11" s="120"/>
-      <c r="J11" s="120"/>
-      <c r="K11" s="120"/>
-      <c r="L11" s="120"/>
-      <c r="M11" s="120"/>
-      <c r="N11" s="120"/>
-      <c r="O11" s="120"/>
-      <c r="P11" s="120"/>
-      <c r="Q11" s="120"/>
-      <c r="R11" s="120"/>
-      <c r="S11" s="120"/>
-      <c r="T11" s="120"/>
-      <c r="U11" s="120"/>
-      <c r="V11" s="120" t="s">
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="115"/>
+      <c r="L11" s="115"/>
+      <c r="M11" s="115"/>
+      <c r="N11" s="115"/>
+      <c r="O11" s="115"/>
+      <c r="P11" s="115"/>
+      <c r="Q11" s="115"/>
+      <c r="R11" s="115"/>
+      <c r="S11" s="115"/>
+      <c r="T11" s="115"/>
+      <c r="U11" s="115"/>
+      <c r="V11" s="115" t="s">
         <v>293</v>
       </c>
-      <c r="W11" s="120"/>
-      <c r="X11" s="120"/>
-      <c r="Y11" s="120"/>
-      <c r="Z11" s="120"/>
-      <c r="AA11" s="120"/>
-      <c r="AB11" s="120"/>
-      <c r="AC11" s="120"/>
-      <c r="AD11" s="120"/>
-      <c r="AE11" s="120"/>
-      <c r="AF11" s="120"/>
-      <c r="AG11" s="120"/>
-      <c r="AH11" s="120"/>
-      <c r="AI11" s="120"/>
-      <c r="AJ11" s="120"/>
-      <c r="AK11" s="120"/>
-      <c r="AL11" s="120"/>
-      <c r="AM11" s="120"/>
-      <c r="AN11" s="120"/>
-      <c r="AO11" s="120"/>
-      <c r="AP11" s="120"/>
-      <c r="AQ11" s="120"/>
-      <c r="AR11" s="120"/>
-      <c r="AS11" s="120"/>
-      <c r="AT11" s="120"/>
-      <c r="AU11" s="120"/>
-      <c r="AV11" s="120"/>
-      <c r="AZ11" s="117" t="s">
+      <c r="W11" s="115"/>
+      <c r="X11" s="115"/>
+      <c r="Y11" s="115"/>
+      <c r="Z11" s="115"/>
+      <c r="AA11" s="115"/>
+      <c r="AB11" s="115"/>
+      <c r="AC11" s="115"/>
+      <c r="AD11" s="115"/>
+      <c r="AE11" s="115"/>
+      <c r="AF11" s="115"/>
+      <c r="AG11" s="115"/>
+      <c r="AH11" s="115"/>
+      <c r="AI11" s="115"/>
+      <c r="AJ11" s="115"/>
+      <c r="AK11" s="115"/>
+      <c r="AL11" s="115"/>
+      <c r="AM11" s="115"/>
+      <c r="AN11" s="115"/>
+      <c r="AO11" s="115"/>
+      <c r="AP11" s="115"/>
+      <c r="AQ11" s="115"/>
+      <c r="AR11" s="115"/>
+      <c r="AS11" s="115"/>
+      <c r="AT11" s="115"/>
+      <c r="AU11" s="115"/>
+      <c r="AV11" s="115"/>
+      <c r="AZ11" s="120" t="s">
         <v>327</v>
       </c>
-      <c r="BA11" s="117"/>
-      <c r="BB11" s="117"/>
-      <c r="BC11" s="117"/>
-      <c r="BD11" s="117"/>
-      <c r="BE11" s="116" t="s">
+      <c r="BA11" s="120"/>
+      <c r="BB11" s="120"/>
+      <c r="BC11" s="120"/>
+      <c r="BD11" s="120"/>
+      <c r="BE11" s="119" t="s">
         <v>339</v>
       </c>
-      <c r="BF11" s="116"/>
-      <c r="BG11" s="116"/>
-      <c r="BH11" s="116"/>
-      <c r="BI11" s="116"/>
-      <c r="BJ11" s="116"/>
-      <c r="BK11" s="116"/>
-      <c r="BL11" s="116"/>
-      <c r="BM11" s="116"/>
-      <c r="BN11" s="116" t="s">
+      <c r="BF11" s="119"/>
+      <c r="BG11" s="119"/>
+      <c r="BH11" s="119"/>
+      <c r="BI11" s="119"/>
+      <c r="BJ11" s="119"/>
+      <c r="BK11" s="119"/>
+      <c r="BL11" s="119"/>
+      <c r="BM11" s="119"/>
+      <c r="BN11" s="119" t="s">
         <v>340</v>
       </c>
-      <c r="BO11" s="116"/>
-      <c r="BP11" s="116"/>
-      <c r="BQ11" s="116"/>
-      <c r="BR11" s="116"/>
-      <c r="BS11" s="116"/>
-      <c r="BT11" s="116"/>
-      <c r="BU11" s="116"/>
-      <c r="BV11" s="116"/>
-      <c r="BW11" s="116"/>
-      <c r="BX11" s="116"/>
-      <c r="BY11" s="116"/>
-      <c r="BZ11" s="116"/>
-      <c r="CA11" s="116"/>
-      <c r="CB11" s="116"/>
+      <c r="BO11" s="119"/>
+      <c r="BP11" s="119"/>
+      <c r="BQ11" s="119"/>
+      <c r="BR11" s="119"/>
+      <c r="BS11" s="119"/>
+      <c r="BT11" s="119"/>
+      <c r="BU11" s="119"/>
+      <c r="BV11" s="119"/>
+      <c r="BW11" s="119"/>
+      <c r="BX11" s="119"/>
+      <c r="BY11" s="119"/>
+      <c r="BZ11" s="119"/>
+      <c r="CA11" s="119"/>
+      <c r="CB11" s="119"/>
     </row>
     <row r="12" spans="4:80" ht="15" customHeight="1">
       <c r="D12" s="118" t="s">
@@ -10749,51 +10749,51 @@
       <c r="E12" s="118"/>
       <c r="F12" s="118"/>
       <c r="G12" s="118"/>
-      <c r="H12" s="121" t="s">
+      <c r="H12" s="117" t="s">
         <v>295</v>
       </c>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="121"/>
-      <c r="P12" s="121"/>
-      <c r="Q12" s="121"/>
-      <c r="R12" s="121"/>
-      <c r="S12" s="121"/>
-      <c r="T12" s="121"/>
-      <c r="U12" s="121"/>
-      <c r="V12" s="120" t="s">
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="117"/>
+      <c r="M12" s="117"/>
+      <c r="N12" s="117"/>
+      <c r="O12" s="117"/>
+      <c r="P12" s="117"/>
+      <c r="Q12" s="117"/>
+      <c r="R12" s="117"/>
+      <c r="S12" s="117"/>
+      <c r="T12" s="117"/>
+      <c r="U12" s="117"/>
+      <c r="V12" s="115" t="s">
         <v>296</v>
       </c>
-      <c r="W12" s="120"/>
-      <c r="X12" s="120"/>
-      <c r="Y12" s="120"/>
-      <c r="Z12" s="120"/>
-      <c r="AA12" s="120"/>
-      <c r="AB12" s="120"/>
-      <c r="AC12" s="120"/>
-      <c r="AD12" s="120"/>
-      <c r="AE12" s="120"/>
-      <c r="AF12" s="120"/>
-      <c r="AG12" s="120"/>
-      <c r="AH12" s="120"/>
-      <c r="AI12" s="120"/>
-      <c r="AJ12" s="120"/>
-      <c r="AK12" s="120"/>
-      <c r="AL12" s="120"/>
-      <c r="AM12" s="120"/>
-      <c r="AN12" s="120"/>
-      <c r="AO12" s="120"/>
-      <c r="AP12" s="120"/>
-      <c r="AQ12" s="120"/>
-      <c r="AR12" s="120"/>
-      <c r="AS12" s="120"/>
-      <c r="AT12" s="120"/>
-      <c r="AU12" s="120"/>
-      <c r="AV12" s="120"/>
+      <c r="W12" s="115"/>
+      <c r="X12" s="115"/>
+      <c r="Y12" s="115"/>
+      <c r="Z12" s="115"/>
+      <c r="AA12" s="115"/>
+      <c r="AB12" s="115"/>
+      <c r="AC12" s="115"/>
+      <c r="AD12" s="115"/>
+      <c r="AE12" s="115"/>
+      <c r="AF12" s="115"/>
+      <c r="AG12" s="115"/>
+      <c r="AH12" s="115"/>
+      <c r="AI12" s="115"/>
+      <c r="AJ12" s="115"/>
+      <c r="AK12" s="115"/>
+      <c r="AL12" s="115"/>
+      <c r="AM12" s="115"/>
+      <c r="AN12" s="115"/>
+      <c r="AO12" s="115"/>
+      <c r="AP12" s="115"/>
+      <c r="AQ12" s="115"/>
+      <c r="AR12" s="115"/>
+      <c r="AS12" s="115"/>
+      <c r="AT12" s="115"/>
+      <c r="AU12" s="115"/>
+      <c r="AV12" s="115"/>
     </row>
     <row r="13" spans="4:80" ht="15" customHeight="1">
       <c r="D13" s="118" t="s">
@@ -10802,51 +10802,51 @@
       <c r="E13" s="118"/>
       <c r="F13" s="118"/>
       <c r="G13" s="118"/>
-      <c r="H13" s="121" t="s">
+      <c r="H13" s="117" t="s">
         <v>298</v>
       </c>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="121"/>
-      <c r="R13" s="121"/>
-      <c r="S13" s="121"/>
-      <c r="T13" s="121"/>
-      <c r="U13" s="121"/>
-      <c r="V13" s="120" t="s">
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="117"/>
+      <c r="O13" s="117"/>
+      <c r="P13" s="117"/>
+      <c r="Q13" s="117"/>
+      <c r="R13" s="117"/>
+      <c r="S13" s="117"/>
+      <c r="T13" s="117"/>
+      <c r="U13" s="117"/>
+      <c r="V13" s="115" t="s">
         <v>299</v>
       </c>
-      <c r="W13" s="120"/>
-      <c r="X13" s="120"/>
-      <c r="Y13" s="120"/>
-      <c r="Z13" s="120"/>
-      <c r="AA13" s="120"/>
-      <c r="AB13" s="120"/>
-      <c r="AC13" s="120"/>
-      <c r="AD13" s="120"/>
-      <c r="AE13" s="120"/>
-      <c r="AF13" s="120"/>
-      <c r="AG13" s="120"/>
-      <c r="AH13" s="120"/>
-      <c r="AI13" s="120"/>
-      <c r="AJ13" s="120"/>
-      <c r="AK13" s="120"/>
-      <c r="AL13" s="120"/>
-      <c r="AM13" s="120"/>
-      <c r="AN13" s="120"/>
-      <c r="AO13" s="120"/>
-      <c r="AP13" s="120"/>
-      <c r="AQ13" s="120"/>
-      <c r="AR13" s="120"/>
-      <c r="AS13" s="120"/>
-      <c r="AT13" s="120"/>
-      <c r="AU13" s="120"/>
-      <c r="AV13" s="120"/>
+      <c r="W13" s="115"/>
+      <c r="X13" s="115"/>
+      <c r="Y13" s="115"/>
+      <c r="Z13" s="115"/>
+      <c r="AA13" s="115"/>
+      <c r="AB13" s="115"/>
+      <c r="AC13" s="115"/>
+      <c r="AD13" s="115"/>
+      <c r="AE13" s="115"/>
+      <c r="AF13" s="115"/>
+      <c r="AG13" s="115"/>
+      <c r="AH13" s="115"/>
+      <c r="AI13" s="115"/>
+      <c r="AJ13" s="115"/>
+      <c r="AK13" s="115"/>
+      <c r="AL13" s="115"/>
+      <c r="AM13" s="115"/>
+      <c r="AN13" s="115"/>
+      <c r="AO13" s="115"/>
+      <c r="AP13" s="115"/>
+      <c r="AQ13" s="115"/>
+      <c r="AR13" s="115"/>
+      <c r="AS13" s="115"/>
+      <c r="AT13" s="115"/>
+      <c r="AU13" s="115"/>
+      <c r="AV13" s="115"/>
     </row>
     <row r="14" spans="4:80" ht="15" customHeight="1">
       <c r="D14" s="118" t="s">
@@ -10855,51 +10855,51 @@
       <c r="E14" s="118"/>
       <c r="F14" s="118"/>
       <c r="G14" s="118"/>
-      <c r="H14" s="121" t="s">
+      <c r="H14" s="117" t="s">
         <v>301</v>
       </c>
-      <c r="I14" s="121"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="121"/>
-      <c r="Q14" s="121"/>
-      <c r="R14" s="121"/>
-      <c r="S14" s="121"/>
-      <c r="T14" s="121"/>
-      <c r="U14" s="121"/>
-      <c r="V14" s="120" t="s">
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="117"/>
+      <c r="O14" s="117"/>
+      <c r="P14" s="117"/>
+      <c r="Q14" s="117"/>
+      <c r="R14" s="117"/>
+      <c r="S14" s="117"/>
+      <c r="T14" s="117"/>
+      <c r="U14" s="117"/>
+      <c r="V14" s="115" t="s">
         <v>302</v>
       </c>
-      <c r="W14" s="120"/>
-      <c r="X14" s="120"/>
-      <c r="Y14" s="120"/>
-      <c r="Z14" s="120"/>
-      <c r="AA14" s="120"/>
-      <c r="AB14" s="120"/>
-      <c r="AC14" s="120"/>
-      <c r="AD14" s="120"/>
-      <c r="AE14" s="120"/>
-      <c r="AF14" s="120"/>
-      <c r="AG14" s="120"/>
-      <c r="AH14" s="120"/>
-      <c r="AI14" s="120"/>
-      <c r="AJ14" s="120"/>
-      <c r="AK14" s="120"/>
-      <c r="AL14" s="120"/>
-      <c r="AM14" s="120"/>
-      <c r="AN14" s="120"/>
-      <c r="AO14" s="120"/>
-      <c r="AP14" s="120"/>
-      <c r="AQ14" s="120"/>
-      <c r="AR14" s="120"/>
-      <c r="AS14" s="120"/>
-      <c r="AT14" s="120"/>
-      <c r="AU14" s="120"/>
-      <c r="AV14" s="120"/>
+      <c r="W14" s="115"/>
+      <c r="X14" s="115"/>
+      <c r="Y14" s="115"/>
+      <c r="Z14" s="115"/>
+      <c r="AA14" s="115"/>
+      <c r="AB14" s="115"/>
+      <c r="AC14" s="115"/>
+      <c r="AD14" s="115"/>
+      <c r="AE14" s="115"/>
+      <c r="AF14" s="115"/>
+      <c r="AG14" s="115"/>
+      <c r="AH14" s="115"/>
+      <c r="AI14" s="115"/>
+      <c r="AJ14" s="115"/>
+      <c r="AK14" s="115"/>
+      <c r="AL14" s="115"/>
+      <c r="AM14" s="115"/>
+      <c r="AN14" s="115"/>
+      <c r="AO14" s="115"/>
+      <c r="AP14" s="115"/>
+      <c r="AQ14" s="115"/>
+      <c r="AR14" s="115"/>
+      <c r="AS14" s="115"/>
+      <c r="AT14" s="115"/>
+      <c r="AU14" s="115"/>
+      <c r="AV14" s="115"/>
     </row>
     <row r="15" spans="4:80" ht="15" customHeight="1">
       <c r="D15" s="118" t="s">
@@ -10908,51 +10908,51 @@
       <c r="E15" s="118"/>
       <c r="F15" s="118"/>
       <c r="G15" s="118"/>
-      <c r="H15" s="120" t="s">
+      <c r="H15" s="115" t="s">
         <v>304</v>
       </c>
-      <c r="I15" s="120"/>
-      <c r="J15" s="120"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="120"/>
-      <c r="P15" s="120"/>
-      <c r="Q15" s="120"/>
-      <c r="R15" s="120"/>
-      <c r="S15" s="120"/>
-      <c r="T15" s="120"/>
-      <c r="U15" s="120"/>
-      <c r="V15" s="120" t="s">
+      <c r="I15" s="115"/>
+      <c r="J15" s="115"/>
+      <c r="K15" s="115"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="115"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="115"/>
+      <c r="P15" s="115"/>
+      <c r="Q15" s="115"/>
+      <c r="R15" s="115"/>
+      <c r="S15" s="115"/>
+      <c r="T15" s="115"/>
+      <c r="U15" s="115"/>
+      <c r="V15" s="115" t="s">
         <v>305</v>
       </c>
-      <c r="W15" s="120"/>
-      <c r="X15" s="120"/>
-      <c r="Y15" s="120"/>
-      <c r="Z15" s="120"/>
-      <c r="AA15" s="120"/>
-      <c r="AB15" s="120"/>
-      <c r="AC15" s="120"/>
-      <c r="AD15" s="120"/>
-      <c r="AE15" s="120"/>
-      <c r="AF15" s="120"/>
-      <c r="AG15" s="120"/>
-      <c r="AH15" s="120"/>
-      <c r="AI15" s="120"/>
-      <c r="AJ15" s="120"/>
-      <c r="AK15" s="120"/>
-      <c r="AL15" s="120"/>
-      <c r="AM15" s="120"/>
-      <c r="AN15" s="120"/>
-      <c r="AO15" s="120"/>
-      <c r="AP15" s="120"/>
-      <c r="AQ15" s="120"/>
-      <c r="AR15" s="120"/>
-      <c r="AS15" s="120"/>
-      <c r="AT15" s="120"/>
-      <c r="AU15" s="120"/>
-      <c r="AV15" s="120"/>
+      <c r="W15" s="115"/>
+      <c r="X15" s="115"/>
+      <c r="Y15" s="115"/>
+      <c r="Z15" s="115"/>
+      <c r="AA15" s="115"/>
+      <c r="AB15" s="115"/>
+      <c r="AC15" s="115"/>
+      <c r="AD15" s="115"/>
+      <c r="AE15" s="115"/>
+      <c r="AF15" s="115"/>
+      <c r="AG15" s="115"/>
+      <c r="AH15" s="115"/>
+      <c r="AI15" s="115"/>
+      <c r="AJ15" s="115"/>
+      <c r="AK15" s="115"/>
+      <c r="AL15" s="115"/>
+      <c r="AM15" s="115"/>
+      <c r="AN15" s="115"/>
+      <c r="AO15" s="115"/>
+      <c r="AP15" s="115"/>
+      <c r="AQ15" s="115"/>
+      <c r="AR15" s="115"/>
+      <c r="AS15" s="115"/>
+      <c r="AT15" s="115"/>
+      <c r="AU15" s="115"/>
+      <c r="AV15" s="115"/>
     </row>
     <row r="16" spans="4:80" ht="15" customHeight="1">
       <c r="D16" s="118" t="s">
@@ -10961,51 +10961,51 @@
       <c r="E16" s="118"/>
       <c r="F16" s="118"/>
       <c r="G16" s="118"/>
-      <c r="H16" s="120" t="s">
+      <c r="H16" s="115" t="s">
         <v>307</v>
       </c>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="120"/>
-      <c r="P16" s="120"/>
-      <c r="Q16" s="120"/>
-      <c r="R16" s="120"/>
-      <c r="S16" s="120"/>
-      <c r="T16" s="120"/>
-      <c r="U16" s="120"/>
-      <c r="V16" s="120" t="s">
+      <c r="I16" s="115"/>
+      <c r="J16" s="115"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="115"/>
+      <c r="R16" s="115"/>
+      <c r="S16" s="115"/>
+      <c r="T16" s="115"/>
+      <c r="U16" s="115"/>
+      <c r="V16" s="115" t="s">
         <v>308</v>
       </c>
-      <c r="W16" s="120"/>
-      <c r="X16" s="120"/>
-      <c r="Y16" s="120"/>
-      <c r="Z16" s="120"/>
-      <c r="AA16" s="120"/>
-      <c r="AB16" s="120"/>
-      <c r="AC16" s="120"/>
-      <c r="AD16" s="120"/>
-      <c r="AE16" s="120"/>
-      <c r="AF16" s="120"/>
-      <c r="AG16" s="120"/>
-      <c r="AH16" s="120"/>
-      <c r="AI16" s="120"/>
-      <c r="AJ16" s="120"/>
-      <c r="AK16" s="120"/>
-      <c r="AL16" s="120"/>
-      <c r="AM16" s="120"/>
-      <c r="AN16" s="120"/>
-      <c r="AO16" s="120"/>
-      <c r="AP16" s="120"/>
-      <c r="AQ16" s="120"/>
-      <c r="AR16" s="120"/>
-      <c r="AS16" s="120"/>
-      <c r="AT16" s="120"/>
-      <c r="AU16" s="120"/>
-      <c r="AV16" s="120"/>
+      <c r="W16" s="115"/>
+      <c r="X16" s="115"/>
+      <c r="Y16" s="115"/>
+      <c r="Z16" s="115"/>
+      <c r="AA16" s="115"/>
+      <c r="AB16" s="115"/>
+      <c r="AC16" s="115"/>
+      <c r="AD16" s="115"/>
+      <c r="AE16" s="115"/>
+      <c r="AF16" s="115"/>
+      <c r="AG16" s="115"/>
+      <c r="AH16" s="115"/>
+      <c r="AI16" s="115"/>
+      <c r="AJ16" s="115"/>
+      <c r="AK16" s="115"/>
+      <c r="AL16" s="115"/>
+      <c r="AM16" s="115"/>
+      <c r="AN16" s="115"/>
+      <c r="AO16" s="115"/>
+      <c r="AP16" s="115"/>
+      <c r="AQ16" s="115"/>
+      <c r="AR16" s="115"/>
+      <c r="AS16" s="115"/>
+      <c r="AT16" s="115"/>
+      <c r="AU16" s="115"/>
+      <c r="AV16" s="115"/>
     </row>
     <row r="17" spans="1:48" ht="15" customHeight="1">
       <c r="D17" s="118" t="s">
@@ -11014,51 +11014,51 @@
       <c r="E17" s="118"/>
       <c r="F17" s="118"/>
       <c r="G17" s="118"/>
-      <c r="H17" s="121" t="s">
+      <c r="H17" s="117" t="s">
         <v>310</v>
       </c>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
-      <c r="P17" s="121"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="121"/>
-      <c r="S17" s="121"/>
-      <c r="T17" s="121"/>
-      <c r="U17" s="121"/>
-      <c r="V17" s="120" t="s">
+      <c r="I17" s="117"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="117"/>
+      <c r="M17" s="117"/>
+      <c r="N17" s="117"/>
+      <c r="O17" s="117"/>
+      <c r="P17" s="117"/>
+      <c r="Q17" s="117"/>
+      <c r="R17" s="117"/>
+      <c r="S17" s="117"/>
+      <c r="T17" s="117"/>
+      <c r="U17" s="117"/>
+      <c r="V17" s="115" t="s">
         <v>311</v>
       </c>
-      <c r="W17" s="120"/>
-      <c r="X17" s="120"/>
-      <c r="Y17" s="120"/>
-      <c r="Z17" s="120"/>
-      <c r="AA17" s="120"/>
-      <c r="AB17" s="120"/>
-      <c r="AC17" s="120"/>
-      <c r="AD17" s="120"/>
-      <c r="AE17" s="120"/>
-      <c r="AF17" s="120"/>
-      <c r="AG17" s="120"/>
-      <c r="AH17" s="120"/>
-      <c r="AI17" s="120"/>
-      <c r="AJ17" s="120"/>
-      <c r="AK17" s="120"/>
-      <c r="AL17" s="120"/>
-      <c r="AM17" s="120"/>
-      <c r="AN17" s="120"/>
-      <c r="AO17" s="120"/>
-      <c r="AP17" s="120"/>
-      <c r="AQ17" s="120"/>
-      <c r="AR17" s="120"/>
-      <c r="AS17" s="120"/>
-      <c r="AT17" s="120"/>
-      <c r="AU17" s="120"/>
-      <c r="AV17" s="120"/>
+      <c r="W17" s="115"/>
+      <c r="X17" s="115"/>
+      <c r="Y17" s="115"/>
+      <c r="Z17" s="115"/>
+      <c r="AA17" s="115"/>
+      <c r="AB17" s="115"/>
+      <c r="AC17" s="115"/>
+      <c r="AD17" s="115"/>
+      <c r="AE17" s="115"/>
+      <c r="AF17" s="115"/>
+      <c r="AG17" s="115"/>
+      <c r="AH17" s="115"/>
+      <c r="AI17" s="115"/>
+      <c r="AJ17" s="115"/>
+      <c r="AK17" s="115"/>
+      <c r="AL17" s="115"/>
+      <c r="AM17" s="115"/>
+      <c r="AN17" s="115"/>
+      <c r="AO17" s="115"/>
+      <c r="AP17" s="115"/>
+      <c r="AQ17" s="115"/>
+      <c r="AR17" s="115"/>
+      <c r="AS17" s="115"/>
+      <c r="AT17" s="115"/>
+      <c r="AU17" s="115"/>
+      <c r="AV17" s="115"/>
     </row>
     <row r="18" spans="1:48" ht="15" customHeight="1">
       <c r="D18" s="118" t="s">
@@ -11067,51 +11067,51 @@
       <c r="E18" s="118"/>
       <c r="F18" s="118"/>
       <c r="G18" s="118"/>
-      <c r="H18" s="120" t="s">
+      <c r="H18" s="115" t="s">
         <v>313</v>
       </c>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="120"/>
-      <c r="L18" s="120"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="120"/>
-      <c r="O18" s="120"/>
-      <c r="P18" s="120"/>
-      <c r="Q18" s="120"/>
-      <c r="R18" s="120"/>
-      <c r="S18" s="120"/>
-      <c r="T18" s="120"/>
-      <c r="U18" s="120"/>
-      <c r="V18" s="120" t="s">
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="115"/>
+      <c r="N18" s="115"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="115"/>
+      <c r="Q18" s="115"/>
+      <c r="R18" s="115"/>
+      <c r="S18" s="115"/>
+      <c r="T18" s="115"/>
+      <c r="U18" s="115"/>
+      <c r="V18" s="115" t="s">
         <v>314</v>
       </c>
-      <c r="W18" s="120"/>
-      <c r="X18" s="120"/>
-      <c r="Y18" s="120"/>
-      <c r="Z18" s="120"/>
-      <c r="AA18" s="120"/>
-      <c r="AB18" s="120"/>
-      <c r="AC18" s="120"/>
-      <c r="AD18" s="120"/>
-      <c r="AE18" s="120"/>
-      <c r="AF18" s="120"/>
-      <c r="AG18" s="120"/>
-      <c r="AH18" s="120"/>
-      <c r="AI18" s="120"/>
-      <c r="AJ18" s="120"/>
-      <c r="AK18" s="120"/>
-      <c r="AL18" s="120"/>
-      <c r="AM18" s="120"/>
-      <c r="AN18" s="120"/>
-      <c r="AO18" s="120"/>
-      <c r="AP18" s="120"/>
-      <c r="AQ18" s="120"/>
-      <c r="AR18" s="120"/>
-      <c r="AS18" s="120"/>
-      <c r="AT18" s="120"/>
-      <c r="AU18" s="120"/>
-      <c r="AV18" s="120"/>
+      <c r="W18" s="115"/>
+      <c r="X18" s="115"/>
+      <c r="Y18" s="115"/>
+      <c r="Z18" s="115"/>
+      <c r="AA18" s="115"/>
+      <c r="AB18" s="115"/>
+      <c r="AC18" s="115"/>
+      <c r="AD18" s="115"/>
+      <c r="AE18" s="115"/>
+      <c r="AF18" s="115"/>
+      <c r="AG18" s="115"/>
+      <c r="AH18" s="115"/>
+      <c r="AI18" s="115"/>
+      <c r="AJ18" s="115"/>
+      <c r="AK18" s="115"/>
+      <c r="AL18" s="115"/>
+      <c r="AM18" s="115"/>
+      <c r="AN18" s="115"/>
+      <c r="AO18" s="115"/>
+      <c r="AP18" s="115"/>
+      <c r="AQ18" s="115"/>
+      <c r="AR18" s="115"/>
+      <c r="AS18" s="115"/>
+      <c r="AT18" s="115"/>
+      <c r="AU18" s="115"/>
+      <c r="AV18" s="115"/>
     </row>
     <row r="19" spans="1:48" ht="15" customHeight="1">
       <c r="D19" s="118" t="s">
@@ -11120,51 +11120,51 @@
       <c r="E19" s="118"/>
       <c r="F19" s="118"/>
       <c r="G19" s="118"/>
-      <c r="H19" s="121" t="s">
+      <c r="H19" s="117" t="s">
         <v>316</v>
       </c>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="121"/>
-      <c r="O19" s="121"/>
-      <c r="P19" s="121"/>
-      <c r="Q19" s="121"/>
-      <c r="R19" s="121"/>
-      <c r="S19" s="121"/>
-      <c r="T19" s="121"/>
-      <c r="U19" s="121"/>
-      <c r="V19" s="120" t="s">
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="117"/>
+      <c r="N19" s="117"/>
+      <c r="O19" s="117"/>
+      <c r="P19" s="117"/>
+      <c r="Q19" s="117"/>
+      <c r="R19" s="117"/>
+      <c r="S19" s="117"/>
+      <c r="T19" s="117"/>
+      <c r="U19" s="117"/>
+      <c r="V19" s="115" t="s">
         <v>317</v>
       </c>
-      <c r="W19" s="120"/>
-      <c r="X19" s="120"/>
-      <c r="Y19" s="120"/>
-      <c r="Z19" s="120"/>
-      <c r="AA19" s="120"/>
-      <c r="AB19" s="120"/>
-      <c r="AC19" s="120"/>
-      <c r="AD19" s="120"/>
-      <c r="AE19" s="120"/>
-      <c r="AF19" s="120"/>
-      <c r="AG19" s="120"/>
-      <c r="AH19" s="120"/>
-      <c r="AI19" s="120"/>
-      <c r="AJ19" s="120"/>
-      <c r="AK19" s="120"/>
-      <c r="AL19" s="120"/>
-      <c r="AM19" s="120"/>
-      <c r="AN19" s="120"/>
-      <c r="AO19" s="120"/>
-      <c r="AP19" s="120"/>
-      <c r="AQ19" s="120"/>
-      <c r="AR19" s="120"/>
-      <c r="AS19" s="120"/>
-      <c r="AT19" s="120"/>
-      <c r="AU19" s="120"/>
-      <c r="AV19" s="120"/>
+      <c r="W19" s="115"/>
+      <c r="X19" s="115"/>
+      <c r="Y19" s="115"/>
+      <c r="Z19" s="115"/>
+      <c r="AA19" s="115"/>
+      <c r="AB19" s="115"/>
+      <c r="AC19" s="115"/>
+      <c r="AD19" s="115"/>
+      <c r="AE19" s="115"/>
+      <c r="AF19" s="115"/>
+      <c r="AG19" s="115"/>
+      <c r="AH19" s="115"/>
+      <c r="AI19" s="115"/>
+      <c r="AJ19" s="115"/>
+      <c r="AK19" s="115"/>
+      <c r="AL19" s="115"/>
+      <c r="AM19" s="115"/>
+      <c r="AN19" s="115"/>
+      <c r="AO19" s="115"/>
+      <c r="AP19" s="115"/>
+      <c r="AQ19" s="115"/>
+      <c r="AR19" s="115"/>
+      <c r="AS19" s="115"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
     </row>
     <row r="20" spans="1:48" ht="15" customHeight="1">
       <c r="D20" s="118" t="s">
@@ -11173,51 +11173,51 @@
       <c r="E20" s="118"/>
       <c r="F20" s="118"/>
       <c r="G20" s="118"/>
-      <c r="H20" s="120" t="s">
+      <c r="H20" s="115" t="s">
         <v>319</v>
       </c>
-      <c r="I20" s="120"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="120"/>
-      <c r="L20" s="120"/>
-      <c r="M20" s="120"/>
-      <c r="N20" s="120"/>
-      <c r="O20" s="120"/>
-      <c r="P20" s="120"/>
-      <c r="Q20" s="120"/>
-      <c r="R20" s="120"/>
-      <c r="S20" s="120"/>
-      <c r="T20" s="120"/>
-      <c r="U20" s="120"/>
-      <c r="V20" s="120" t="s">
+      <c r="I20" s="115"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="115"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="115"/>
+      <c r="N20" s="115"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="115"/>
+      <c r="Q20" s="115"/>
+      <c r="R20" s="115"/>
+      <c r="S20" s="115"/>
+      <c r="T20" s="115"/>
+      <c r="U20" s="115"/>
+      <c r="V20" s="115" t="s">
         <v>320</v>
       </c>
-      <c r="W20" s="120"/>
-      <c r="X20" s="120"/>
-      <c r="Y20" s="120"/>
-      <c r="Z20" s="120"/>
-      <c r="AA20" s="120"/>
-      <c r="AB20" s="120"/>
-      <c r="AC20" s="120"/>
-      <c r="AD20" s="120"/>
-      <c r="AE20" s="120"/>
-      <c r="AF20" s="120"/>
-      <c r="AG20" s="120"/>
-      <c r="AH20" s="120"/>
-      <c r="AI20" s="120"/>
-      <c r="AJ20" s="120"/>
-      <c r="AK20" s="120"/>
-      <c r="AL20" s="120"/>
-      <c r="AM20" s="120"/>
-      <c r="AN20" s="120"/>
-      <c r="AO20" s="120"/>
-      <c r="AP20" s="120"/>
-      <c r="AQ20" s="120"/>
-      <c r="AR20" s="120"/>
-      <c r="AS20" s="120"/>
-      <c r="AT20" s="120"/>
-      <c r="AU20" s="120"/>
-      <c r="AV20" s="120"/>
+      <c r="W20" s="115"/>
+      <c r="X20" s="115"/>
+      <c r="Y20" s="115"/>
+      <c r="Z20" s="115"/>
+      <c r="AA20" s="115"/>
+      <c r="AB20" s="115"/>
+      <c r="AC20" s="115"/>
+      <c r="AD20" s="115"/>
+      <c r="AE20" s="115"/>
+      <c r="AF20" s="115"/>
+      <c r="AG20" s="115"/>
+      <c r="AH20" s="115"/>
+      <c r="AI20" s="115"/>
+      <c r="AJ20" s="115"/>
+      <c r="AK20" s="115"/>
+      <c r="AL20" s="115"/>
+      <c r="AM20" s="115"/>
+      <c r="AN20" s="115"/>
+      <c r="AO20" s="115"/>
+      <c r="AP20" s="115"/>
+      <c r="AQ20" s="115"/>
+      <c r="AR20" s="115"/>
+      <c r="AS20" s="115"/>
+      <c r="AT20" s="115"/>
+      <c r="AU20" s="115"/>
+      <c r="AV20" s="115"/>
     </row>
     <row r="21" spans="1:48" ht="15" customHeight="1">
       <c r="D21" s="118" t="s">
@@ -11226,51 +11226,51 @@
       <c r="E21" s="118"/>
       <c r="F21" s="118"/>
       <c r="G21" s="118"/>
-      <c r="H21" s="121" t="s">
+      <c r="H21" s="117" t="s">
         <v>322</v>
       </c>
-      <c r="I21" s="121"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="121"/>
-      <c r="P21" s="121"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="121"/>
-      <c r="S21" s="121"/>
-      <c r="T21" s="121"/>
-      <c r="U21" s="121"/>
-      <c r="V21" s="120" t="s">
+      <c r="I21" s="117"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="117"/>
+      <c r="N21" s="117"/>
+      <c r="O21" s="117"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="117"/>
+      <c r="R21" s="117"/>
+      <c r="S21" s="117"/>
+      <c r="T21" s="117"/>
+      <c r="U21" s="117"/>
+      <c r="V21" s="115" t="s">
         <v>323</v>
       </c>
-      <c r="W21" s="120"/>
-      <c r="X21" s="120"/>
-      <c r="Y21" s="120"/>
-      <c r="Z21" s="120"/>
-      <c r="AA21" s="120"/>
-      <c r="AB21" s="120"/>
-      <c r="AC21" s="120"/>
-      <c r="AD21" s="120"/>
-      <c r="AE21" s="120"/>
-      <c r="AF21" s="120"/>
-      <c r="AG21" s="120"/>
-      <c r="AH21" s="120"/>
-      <c r="AI21" s="120"/>
-      <c r="AJ21" s="120"/>
-      <c r="AK21" s="120"/>
-      <c r="AL21" s="120"/>
-      <c r="AM21" s="120"/>
-      <c r="AN21" s="120"/>
-      <c r="AO21" s="120"/>
-      <c r="AP21" s="120"/>
-      <c r="AQ21" s="120"/>
-      <c r="AR21" s="120"/>
-      <c r="AS21" s="120"/>
-      <c r="AT21" s="120"/>
-      <c r="AU21" s="120"/>
-      <c r="AV21" s="120"/>
+      <c r="W21" s="115"/>
+      <c r="X21" s="115"/>
+      <c r="Y21" s="115"/>
+      <c r="Z21" s="115"/>
+      <c r="AA21" s="115"/>
+      <c r="AB21" s="115"/>
+      <c r="AC21" s="115"/>
+      <c r="AD21" s="115"/>
+      <c r="AE21" s="115"/>
+      <c r="AF21" s="115"/>
+      <c r="AG21" s="115"/>
+      <c r="AH21" s="115"/>
+      <c r="AI21" s="115"/>
+      <c r="AJ21" s="115"/>
+      <c r="AK21" s="115"/>
+      <c r="AL21" s="115"/>
+      <c r="AM21" s="115"/>
+      <c r="AN21" s="115"/>
+      <c r="AO21" s="115"/>
+      <c r="AP21" s="115"/>
+      <c r="AQ21" s="115"/>
+      <c r="AR21" s="115"/>
+      <c r="AS21" s="115"/>
+      <c r="AT21" s="115"/>
+      <c r="AU21" s="115"/>
+      <c r="AV21" s="115"/>
     </row>
     <row r="22" spans="1:48" s="74" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="D22" s="75"/>
@@ -11704,38 +11704,36 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="V20:AV20"/>
-    <mergeCell ref="V21:AV21"/>
-    <mergeCell ref="V14:AV14"/>
-    <mergeCell ref="V15:AV15"/>
-    <mergeCell ref="V16:AV16"/>
-    <mergeCell ref="V17:AV17"/>
-    <mergeCell ref="V18:AV18"/>
-    <mergeCell ref="V19:AV19"/>
-    <mergeCell ref="V13:AV13"/>
-    <mergeCell ref="V2:AV2"/>
-    <mergeCell ref="V3:AV3"/>
-    <mergeCell ref="V4:AV4"/>
-    <mergeCell ref="V5:AV5"/>
-    <mergeCell ref="V6:AV6"/>
-    <mergeCell ref="V7:AV7"/>
-    <mergeCell ref="V8:AV8"/>
-    <mergeCell ref="V9:AV9"/>
-    <mergeCell ref="V10:AV10"/>
-    <mergeCell ref="V11:AV11"/>
-    <mergeCell ref="V12:AV12"/>
-    <mergeCell ref="H21:U21"/>
-    <mergeCell ref="H10:U10"/>
-    <mergeCell ref="H11:U11"/>
-    <mergeCell ref="H12:U12"/>
-    <mergeCell ref="H13:U13"/>
-    <mergeCell ref="H14:U14"/>
-    <mergeCell ref="H15:U15"/>
-    <mergeCell ref="H16:U16"/>
-    <mergeCell ref="H17:U17"/>
-    <mergeCell ref="H18:U18"/>
-    <mergeCell ref="H19:U19"/>
-    <mergeCell ref="H20:U20"/>
+    <mergeCell ref="BN9:CB9"/>
+    <mergeCell ref="BN10:CB10"/>
+    <mergeCell ref="BN11:CB11"/>
+    <mergeCell ref="AZ11:BD11"/>
+    <mergeCell ref="BE6:BM6"/>
+    <mergeCell ref="BE7:BM7"/>
+    <mergeCell ref="BE8:BM8"/>
+    <mergeCell ref="BE9:BM9"/>
+    <mergeCell ref="BE10:BM10"/>
+    <mergeCell ref="BE11:BM11"/>
+    <mergeCell ref="AZ6:BD6"/>
+    <mergeCell ref="AZ7:BD7"/>
+    <mergeCell ref="AZ8:BD8"/>
+    <mergeCell ref="AZ9:BD9"/>
+    <mergeCell ref="AZ10:BD10"/>
+    <mergeCell ref="BN6:CB6"/>
+    <mergeCell ref="BN7:CB7"/>
+    <mergeCell ref="BN8:CB8"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D12:G12"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="H2:U2"/>
@@ -11752,36 +11750,38 @@
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="BN11:CB11"/>
-    <mergeCell ref="AZ11:BD11"/>
-    <mergeCell ref="BE6:BM6"/>
-    <mergeCell ref="BE7:BM7"/>
-    <mergeCell ref="BE8:BM8"/>
-    <mergeCell ref="BE9:BM9"/>
-    <mergeCell ref="BE10:BM10"/>
-    <mergeCell ref="BE11:BM11"/>
-    <mergeCell ref="AZ6:BD6"/>
-    <mergeCell ref="AZ7:BD7"/>
-    <mergeCell ref="AZ8:BD8"/>
-    <mergeCell ref="AZ9:BD9"/>
-    <mergeCell ref="AZ10:BD10"/>
-    <mergeCell ref="BN6:CB6"/>
-    <mergeCell ref="BN7:CB7"/>
-    <mergeCell ref="BN8:CB8"/>
-    <mergeCell ref="BN9:CB9"/>
-    <mergeCell ref="BN10:CB10"/>
+    <mergeCell ref="H21:U21"/>
+    <mergeCell ref="H10:U10"/>
+    <mergeCell ref="H11:U11"/>
+    <mergeCell ref="H12:U12"/>
+    <mergeCell ref="H13:U13"/>
+    <mergeCell ref="H14:U14"/>
+    <mergeCell ref="H15:U15"/>
+    <mergeCell ref="H16:U16"/>
+    <mergeCell ref="H17:U17"/>
+    <mergeCell ref="H18:U18"/>
+    <mergeCell ref="H19:U19"/>
+    <mergeCell ref="H20:U20"/>
+    <mergeCell ref="V13:AV13"/>
+    <mergeCell ref="V2:AV2"/>
+    <mergeCell ref="V3:AV3"/>
+    <mergeCell ref="V4:AV4"/>
+    <mergeCell ref="V5:AV5"/>
+    <mergeCell ref="V6:AV6"/>
+    <mergeCell ref="V7:AV7"/>
+    <mergeCell ref="V8:AV8"/>
+    <mergeCell ref="V9:AV9"/>
+    <mergeCell ref="V10:AV10"/>
+    <mergeCell ref="V11:AV11"/>
+    <mergeCell ref="V12:AV12"/>
+    <mergeCell ref="V20:AV20"/>
+    <mergeCell ref="V21:AV21"/>
+    <mergeCell ref="V14:AV14"/>
+    <mergeCell ref="V15:AV15"/>
+    <mergeCell ref="V16:AV16"/>
+    <mergeCell ref="V17:AV17"/>
+    <mergeCell ref="V18:AV18"/>
+    <mergeCell ref="V19:AV19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13522,31 +13522,31 @@
       <c r="BA26" s="81"/>
     </row>
     <row r="27" spans="1:53" ht="15" customHeight="1">
-      <c r="D27" s="124" t="s">
+      <c r="D27" s="122" t="s">
         <v>452</v>
       </c>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="124"/>
-      <c r="I27" s="124" t="s">
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="122"/>
+      <c r="I27" s="122" t="s">
         <v>119</v>
       </c>
-      <c r="J27" s="124"/>
-      <c r="K27" s="124"/>
-      <c r="L27" s="124"/>
-      <c r="M27" s="124"/>
-      <c r="N27" s="124"/>
-      <c r="O27" s="124"/>
-      <c r="P27" s="124"/>
-      <c r="Q27" s="124"/>
-      <c r="R27" s="124"/>
-      <c r="S27" s="124"/>
-      <c r="T27" s="124"/>
-      <c r="U27" s="124"/>
-      <c r="V27" s="124"/>
-      <c r="W27" s="124"/>
-      <c r="X27" s="124"/>
+      <c r="J27" s="122"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="122"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="122"/>
+      <c r="R27" s="122"/>
+      <c r="S27" s="122"/>
+      <c r="T27" s="122"/>
+      <c r="U27" s="122"/>
+      <c r="V27" s="122"/>
+      <c r="W27" s="122"/>
+      <c r="X27" s="122"/>
       <c r="AU27" s="81"/>
       <c r="AV27" s="81"/>
       <c r="AW27" s="81"/>
@@ -13563,24 +13563,24 @@
       <c r="F28" s="123"/>
       <c r="G28" s="123"/>
       <c r="H28" s="123"/>
-      <c r="I28" s="122" t="s">
+      <c r="I28" s="124" t="s">
         <v>454</v>
       </c>
-      <c r="J28" s="122"/>
-      <c r="K28" s="122"/>
-      <c r="L28" s="122"/>
-      <c r="M28" s="122"/>
-      <c r="N28" s="122"/>
-      <c r="O28" s="122"/>
-      <c r="P28" s="122"/>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="122"/>
-      <c r="S28" s="122"/>
-      <c r="T28" s="122"/>
-      <c r="U28" s="122"/>
-      <c r="V28" s="122"/>
-      <c r="W28" s="122"/>
-      <c r="X28" s="122"/>
+      <c r="J28" s="124"/>
+      <c r="K28" s="124"/>
+      <c r="L28" s="124"/>
+      <c r="M28" s="124"/>
+      <c r="N28" s="124"/>
+      <c r="O28" s="124"/>
+      <c r="P28" s="124"/>
+      <c r="Q28" s="124"/>
+      <c r="R28" s="124"/>
+      <c r="S28" s="124"/>
+      <c r="T28" s="124"/>
+      <c r="U28" s="124"/>
+      <c r="V28" s="124"/>
+      <c r="W28" s="124"/>
+      <c r="X28" s="124"/>
       <c r="AU28" s="81"/>
       <c r="AV28" s="81"/>
       <c r="AW28" s="81"/>
@@ -13597,24 +13597,24 @@
       <c r="F29" s="123"/>
       <c r="G29" s="123"/>
       <c r="H29" s="123"/>
-      <c r="I29" s="122" t="s">
+      <c r="I29" s="124" t="s">
         <v>456</v>
       </c>
-      <c r="J29" s="122"/>
-      <c r="K29" s="122"/>
-      <c r="L29" s="122"/>
-      <c r="M29" s="122"/>
-      <c r="N29" s="122"/>
-      <c r="O29" s="122"/>
-      <c r="P29" s="122"/>
-      <c r="Q29" s="122"/>
-      <c r="R29" s="122"/>
-      <c r="S29" s="122"/>
-      <c r="T29" s="122"/>
-      <c r="U29" s="122"/>
-      <c r="V29" s="122"/>
-      <c r="W29" s="122"/>
-      <c r="X29" s="122"/>
+      <c r="J29" s="124"/>
+      <c r="K29" s="124"/>
+      <c r="L29" s="124"/>
+      <c r="M29" s="124"/>
+      <c r="N29" s="124"/>
+      <c r="O29" s="124"/>
+      <c r="P29" s="124"/>
+      <c r="Q29" s="124"/>
+      <c r="R29" s="124"/>
+      <c r="S29" s="124"/>
+      <c r="T29" s="124"/>
+      <c r="U29" s="124"/>
+      <c r="V29" s="124"/>
+      <c r="W29" s="124"/>
+      <c r="X29" s="124"/>
       <c r="AU29" s="81"/>
       <c r="AV29" s="81"/>
       <c r="AW29" s="81"/>
@@ -13631,24 +13631,24 @@
       <c r="F30" s="123"/>
       <c r="G30" s="123"/>
       <c r="H30" s="123"/>
-      <c r="I30" s="122" t="s">
+      <c r="I30" s="124" t="s">
         <v>458</v>
       </c>
-      <c r="J30" s="122"/>
-      <c r="K30" s="122"/>
-      <c r="L30" s="122"/>
-      <c r="M30" s="122"/>
-      <c r="N30" s="122"/>
-      <c r="O30" s="122"/>
-      <c r="P30" s="122"/>
-      <c r="Q30" s="122"/>
-      <c r="R30" s="122"/>
-      <c r="S30" s="122"/>
-      <c r="T30" s="122"/>
-      <c r="U30" s="122"/>
-      <c r="V30" s="122"/>
-      <c r="W30" s="122"/>
-      <c r="X30" s="122"/>
+      <c r="J30" s="124"/>
+      <c r="K30" s="124"/>
+      <c r="L30" s="124"/>
+      <c r="M30" s="124"/>
+      <c r="N30" s="124"/>
+      <c r="O30" s="124"/>
+      <c r="P30" s="124"/>
+      <c r="Q30" s="124"/>
+      <c r="R30" s="124"/>
+      <c r="S30" s="124"/>
+      <c r="T30" s="124"/>
+      <c r="U30" s="124"/>
+      <c r="V30" s="124"/>
+      <c r="W30" s="124"/>
+      <c r="X30" s="124"/>
       <c r="AU30" s="81"/>
       <c r="AV30" s="81"/>
       <c r="AW30" s="81"/>
@@ -13665,24 +13665,24 @@
       <c r="F31" s="123"/>
       <c r="G31" s="123"/>
       <c r="H31" s="123"/>
-      <c r="I31" s="122" t="s">
+      <c r="I31" s="124" t="s">
         <v>460</v>
       </c>
-      <c r="J31" s="122"/>
-      <c r="K31" s="122"/>
-      <c r="L31" s="122"/>
-      <c r="M31" s="122"/>
-      <c r="N31" s="122"/>
-      <c r="O31" s="122"/>
-      <c r="P31" s="122"/>
-      <c r="Q31" s="122"/>
-      <c r="R31" s="122"/>
-      <c r="S31" s="122"/>
-      <c r="T31" s="122"/>
-      <c r="U31" s="122"/>
-      <c r="V31" s="122"/>
-      <c r="W31" s="122"/>
-      <c r="X31" s="122"/>
+      <c r="J31" s="124"/>
+      <c r="K31" s="124"/>
+      <c r="L31" s="124"/>
+      <c r="M31" s="124"/>
+      <c r="N31" s="124"/>
+      <c r="O31" s="124"/>
+      <c r="P31" s="124"/>
+      <c r="Q31" s="124"/>
+      <c r="R31" s="124"/>
+      <c r="S31" s="124"/>
+      <c r="T31" s="124"/>
+      <c r="U31" s="124"/>
+      <c r="V31" s="124"/>
+      <c r="W31" s="124"/>
+      <c r="X31" s="124"/>
       <c r="AU31" s="81"/>
       <c r="AV31" s="81"/>
       <c r="AW31" s="81"/>
@@ -13935,31 +13935,31 @@
       <c r="BA51" s="81"/>
     </row>
     <row r="52" spans="1:53" ht="15" customHeight="1">
-      <c r="C52" s="124" t="s">
+      <c r="C52" s="122" t="s">
         <v>452</v>
       </c>
-      <c r="D52" s="124"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="124"/>
-      <c r="G52" s="124"/>
-      <c r="H52" s="124"/>
-      <c r="I52" s="124" t="s">
+      <c r="D52" s="122"/>
+      <c r="E52" s="122"/>
+      <c r="F52" s="122"/>
+      <c r="G52" s="122"/>
+      <c r="H52" s="122"/>
+      <c r="I52" s="122" t="s">
         <v>119</v>
       </c>
-      <c r="J52" s="124"/>
-      <c r="K52" s="124"/>
-      <c r="L52" s="124"/>
-      <c r="M52" s="124"/>
-      <c r="N52" s="124"/>
-      <c r="O52" s="124"/>
-      <c r="P52" s="124"/>
-      <c r="Q52" s="124"/>
-      <c r="R52" s="124"/>
-      <c r="S52" s="124"/>
-      <c r="T52" s="124"/>
-      <c r="U52" s="124"/>
-      <c r="V52" s="124"/>
-      <c r="W52" s="124"/>
+      <c r="J52" s="122"/>
+      <c r="K52" s="122"/>
+      <c r="L52" s="122"/>
+      <c r="M52" s="122"/>
+      <c r="N52" s="122"/>
+      <c r="O52" s="122"/>
+      <c r="P52" s="122"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="122"/>
+      <c r="S52" s="122"/>
+      <c r="T52" s="122"/>
+      <c r="U52" s="122"/>
+      <c r="V52" s="122"/>
+      <c r="W52" s="122"/>
       <c r="AU52" s="81"/>
       <c r="AV52" s="81"/>
       <c r="AW52" s="81"/>
@@ -13977,23 +13977,23 @@
       <c r="F53" s="123"/>
       <c r="G53" s="123"/>
       <c r="H53" s="123"/>
-      <c r="I53" s="122" t="s">
+      <c r="I53" s="124" t="s">
         <v>470</v>
       </c>
-      <c r="J53" s="122"/>
-      <c r="K53" s="122"/>
-      <c r="L53" s="122"/>
-      <c r="M53" s="122"/>
-      <c r="N53" s="122"/>
-      <c r="O53" s="122"/>
-      <c r="P53" s="122"/>
-      <c r="Q53" s="122"/>
-      <c r="R53" s="122"/>
-      <c r="S53" s="122"/>
-      <c r="T53" s="122"/>
-      <c r="U53" s="122"/>
-      <c r="V53" s="122"/>
-      <c r="W53" s="122"/>
+      <c r="J53" s="124"/>
+      <c r="K53" s="124"/>
+      <c r="L53" s="124"/>
+      <c r="M53" s="124"/>
+      <c r="N53" s="124"/>
+      <c r="O53" s="124"/>
+      <c r="P53" s="124"/>
+      <c r="Q53" s="124"/>
+      <c r="R53" s="124"/>
+      <c r="S53" s="124"/>
+      <c r="T53" s="124"/>
+      <c r="U53" s="124"/>
+      <c r="V53" s="124"/>
+      <c r="W53" s="124"/>
       <c r="AU53" s="81"/>
       <c r="AV53" s="81"/>
       <c r="AW53" s="81"/>
@@ -14011,23 +14011,23 @@
       <c r="F54" s="123"/>
       <c r="G54" s="123"/>
       <c r="H54" s="123"/>
-      <c r="I54" s="122" t="s">
+      <c r="I54" s="124" t="s">
         <v>472</v>
       </c>
-      <c r="J54" s="122"/>
-      <c r="K54" s="122"/>
-      <c r="L54" s="122"/>
-      <c r="M54" s="122"/>
-      <c r="N54" s="122"/>
-      <c r="O54" s="122"/>
-      <c r="P54" s="122"/>
-      <c r="Q54" s="122"/>
-      <c r="R54" s="122"/>
-      <c r="S54" s="122"/>
-      <c r="T54" s="122"/>
-      <c r="U54" s="122"/>
-      <c r="V54" s="122"/>
-      <c r="W54" s="122"/>
+      <c r="J54" s="124"/>
+      <c r="K54" s="124"/>
+      <c r="L54" s="124"/>
+      <c r="M54" s="124"/>
+      <c r="N54" s="124"/>
+      <c r="O54" s="124"/>
+      <c r="P54" s="124"/>
+      <c r="Q54" s="124"/>
+      <c r="R54" s="124"/>
+      <c r="S54" s="124"/>
+      <c r="T54" s="124"/>
+      <c r="U54" s="124"/>
+      <c r="V54" s="124"/>
+      <c r="W54" s="124"/>
       <c r="AU54" s="81"/>
       <c r="AV54" s="81"/>
       <c r="AW54" s="81"/>
@@ -14045,23 +14045,23 @@
       <c r="F55" s="123"/>
       <c r="G55" s="123"/>
       <c r="H55" s="123"/>
-      <c r="I55" s="122" t="s">
+      <c r="I55" s="124" t="s">
         <v>474</v>
       </c>
-      <c r="J55" s="122"/>
-      <c r="K55" s="122"/>
-      <c r="L55" s="122"/>
-      <c r="M55" s="122"/>
-      <c r="N55" s="122"/>
-      <c r="O55" s="122"/>
-      <c r="P55" s="122"/>
-      <c r="Q55" s="122"/>
-      <c r="R55" s="122"/>
-      <c r="S55" s="122"/>
-      <c r="T55" s="122"/>
-      <c r="U55" s="122"/>
-      <c r="V55" s="122"/>
-      <c r="W55" s="122"/>
+      <c r="J55" s="124"/>
+      <c r="K55" s="124"/>
+      <c r="L55" s="124"/>
+      <c r="M55" s="124"/>
+      <c r="N55" s="124"/>
+      <c r="O55" s="124"/>
+      <c r="P55" s="124"/>
+      <c r="Q55" s="124"/>
+      <c r="R55" s="124"/>
+      <c r="S55" s="124"/>
+      <c r="T55" s="124"/>
+      <c r="U55" s="124"/>
+      <c r="V55" s="124"/>
+      <c r="W55" s="124"/>
       <c r="AU55" s="81"/>
       <c r="AV55" s="81"/>
       <c r="AW55" s="81"/>
@@ -14079,23 +14079,23 @@
       <c r="F56" s="123"/>
       <c r="G56" s="123"/>
       <c r="H56" s="123"/>
-      <c r="I56" s="122" t="s">
+      <c r="I56" s="124" t="s">
         <v>475</v>
       </c>
-      <c r="J56" s="122"/>
-      <c r="K56" s="122"/>
-      <c r="L56" s="122"/>
-      <c r="M56" s="122"/>
-      <c r="N56" s="122"/>
-      <c r="O56" s="122"/>
-      <c r="P56" s="122"/>
-      <c r="Q56" s="122"/>
-      <c r="R56" s="122"/>
-      <c r="S56" s="122"/>
-      <c r="T56" s="122"/>
-      <c r="U56" s="122"/>
-      <c r="V56" s="122"/>
-      <c r="W56" s="122"/>
+      <c r="J56" s="124"/>
+      <c r="K56" s="124"/>
+      <c r="L56" s="124"/>
+      <c r="M56" s="124"/>
+      <c r="N56" s="124"/>
+      <c r="O56" s="124"/>
+      <c r="P56" s="124"/>
+      <c r="Q56" s="124"/>
+      <c r="R56" s="124"/>
+      <c r="S56" s="124"/>
+      <c r="T56" s="124"/>
+      <c r="U56" s="124"/>
+      <c r="V56" s="124"/>
+      <c r="W56" s="124"/>
       <c r="AU56" s="81"/>
       <c r="AV56" s="81"/>
       <c r="AW56" s="81"/>
@@ -14113,23 +14113,23 @@
       <c r="F57" s="123"/>
       <c r="G57" s="123"/>
       <c r="H57" s="123"/>
-      <c r="I57" s="122" t="s">
+      <c r="I57" s="124" t="s">
         <v>477</v>
       </c>
-      <c r="J57" s="122"/>
-      <c r="K57" s="122"/>
-      <c r="L57" s="122"/>
-      <c r="M57" s="122"/>
-      <c r="N57" s="122"/>
-      <c r="O57" s="122"/>
-      <c r="P57" s="122"/>
-      <c r="Q57" s="122"/>
-      <c r="R57" s="122"/>
-      <c r="S57" s="122"/>
-      <c r="T57" s="122"/>
-      <c r="U57" s="122"/>
-      <c r="V57" s="122"/>
-      <c r="W57" s="122"/>
+      <c r="J57" s="124"/>
+      <c r="K57" s="124"/>
+      <c r="L57" s="124"/>
+      <c r="M57" s="124"/>
+      <c r="N57" s="124"/>
+      <c r="O57" s="124"/>
+      <c r="P57" s="124"/>
+      <c r="Q57" s="124"/>
+      <c r="R57" s="124"/>
+      <c r="S57" s="124"/>
+      <c r="T57" s="124"/>
+      <c r="U57" s="124"/>
+      <c r="V57" s="124"/>
+      <c r="W57" s="124"/>
       <c r="AU57" s="81"/>
       <c r="AV57" s="81"/>
       <c r="AW57" s="81"/>
@@ -14695,16 +14695,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="I27:X27"/>
-    <mergeCell ref="I28:X28"/>
-    <mergeCell ref="I29:X29"/>
-    <mergeCell ref="I30:X30"/>
-    <mergeCell ref="I31:X31"/>
     <mergeCell ref="I55:W55"/>
     <mergeCell ref="I56:W56"/>
     <mergeCell ref="I57:W57"/>
@@ -14717,6 +14707,16 @@
     <mergeCell ref="C54:H54"/>
     <mergeCell ref="C55:H55"/>
     <mergeCell ref="C56:H56"/>
+    <mergeCell ref="I27:X27"/>
+    <mergeCell ref="I28:X28"/>
+    <mergeCell ref="I29:X29"/>
+    <mergeCell ref="I30:X30"/>
+    <mergeCell ref="I31:X31"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -15265,21 +15265,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
     <mergeCell ref="E83:H83"/>
     <mergeCell ref="E84:H84"/>
     <mergeCell ref="E85:H85"/>
     <mergeCell ref="E86:H86"/>
     <mergeCell ref="E87:H87"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I87:K87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
